--- a/.source/kb023_insurance.xlsx
+++ b/.source/kb023_insurance.xlsx
@@ -926,9 +926,9 @@
           <t>751208-1654415</t>
         </is>
       </c>
-      <c r="C7" s="0" t="n"/>
-      <c r="D7" s="0" t="n"/>
-      <c r="E7" s="0" t="n"/>
+      <c r="C7" s="0" t="inlineStr"/>
+      <c r="D7" s="0" t="inlineStr"/>
+      <c r="E7" s="0" t="inlineStr"/>
       <c r="F7" s="0" t="inlineStr">
         <is>
           <t>(무)LIG행복한인생</t>
@@ -964,7 +964,7 @@
       <c r="N7" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="0" t="n"/>
+      <c r="O7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="16.5" customHeight="1" s="4">
       <c r="A8" s="0" t="inlineStr">
